--- a/sources/table_normalization/xlsx/economy-table53.xlsx
+++ b/sources/table_normalization/xlsx/economy-table53.xlsx
@@ -264,7 +264,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -573,7 +573,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -590,6 +590,7 @@
     <col min="9" max="9" width="14.08984375" customWidth="1"/>
     <col min="13" max="13" width="9.7265625" customWidth="1"/>
     <col min="15" max="15" width="10.6328125" customWidth="1"/>
+    <col min="17" max="17" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
